--- a/Perth_SC_GPS_Weekly_Update_v3.xlsx
+++ b/Perth_SC_GPS_Weekly_Update_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thali/Desktop/Perth_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37402A4B-EE46-B64C-8A12-3CA00D92EECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41535D13-C404-E144-8973-EAFDA1B8524E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GPS Data" sheetId="1" r:id="rId1"/>
@@ -547,20 +547,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1967,52 +1967,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
       <c r="J5" s="4" t="s">
         <v>4</v>
       </c>
@@ -2616,14 +2616,14 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
@@ -2800,14 +2800,14 @@
       <c r="H45" s="21"/>
     </row>
     <row r="52" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="28"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
     </row>
@@ -2975,12 +2975,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:G22">
     <cfRule type="dataBar" priority="1">
@@ -3025,7 +3025,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>50</v>
       </c>
     </row>

--- a/Perth_SC_GPS_Weekly_Update_v3.xlsx
+++ b/Perth_SC_GPS_Weekly_Update_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thali/Desktop/Perth_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B479A1BF-8881-434C-A09F-AADB7C9D5E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BFF95D-E5BE-1549-8E5A-2076D8EBD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GPS Data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
   <si>
     <t>Perth SC – Senior Women</t>
   </si>
@@ -47,9 +47,6 @@
     <t>GPS Position Comparisons Dashboard</t>
   </si>
   <si>
-    <t>Compare players by soccer role groups: Attackers (8, 9 &amp; 10), Midfielders, and Defenders. Update GPS Data and this dashboard will refresh.</t>
-  </si>
-  <si>
     <t>Attackers (8, 9 &amp; 10)</t>
   </si>
   <si>
@@ -173,9 +170,6 @@
     <t>23/06/2026</t>
   </si>
   <si>
-    <t>Opponent (Game)</t>
-  </si>
-  <si>
     <t>Round (Game)</t>
   </si>
   <si>
@@ -312,6 +306,12 @@
   </si>
   <si>
     <t>FIFA Women's World Cup physical performance analyses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training session </t>
+  </si>
+  <si>
+    <t>Compare players by soccer role groups: Attackers, Midfielders, and Defenders. Update GPS Data and this dashboard will refresh.</t>
   </si>
 </sst>
 </file>
@@ -1062,58 +1062,55 @@
     </row>
     <row r="2" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>42</v>
       </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>43</v>
-      </c>
-      <c r="G4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H6" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>5774.12</v>
@@ -1134,12 +1131,12 @@
         <v>411.35</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>7291.53</v>
@@ -1160,12 +1157,12 @@
         <v>856.36</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>4313.4799999999996</v>
@@ -1186,12 +1183,12 @@
         <v>252.24</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>5911.91</v>
@@ -1212,12 +1209,12 @@
         <v>544.71</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>4101.67</v>
@@ -1238,12 +1235,12 @@
         <v>245.71</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>6950.08</v>
@@ -1264,12 +1261,12 @@
         <v>478.01</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>5939.23</v>
@@ -1290,12 +1287,12 @@
         <v>332.93</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>6476.03</v>
@@ -1316,12 +1313,12 @@
         <v>403.01</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>6997.18</v>
@@ -1342,12 +1339,12 @@
         <v>990.76</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>5992.87</v>
@@ -1368,12 +1365,12 @@
         <v>311.58</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>6066.98</v>
@@ -1394,12 +1391,12 @@
         <v>388.21</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>6342.21</v>
@@ -1420,12 +1417,12 @@
         <v>635.58000000000004</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>6563.66</v>
@@ -1446,12 +1443,12 @@
         <v>792.35</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>7036.88</v>
@@ -1472,12 +1469,12 @@
         <v>981.88</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>6977.62</v>
@@ -1498,12 +1495,12 @@
         <v>862</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>6731.04</v>
@@ -1524,12 +1521,12 @@
         <v>741.36</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>6004.46</v>
@@ -1550,7 +1547,7 @@
         <v>646.20000000000005</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1576,370 +1573,370 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
         <v>36</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1992,7 +1989,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="30" t="s">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -2004,7 +2001,7 @@
     </row>
     <row r="5" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="27" t="s">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -2014,39 +2011,39 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
       <c r="J5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="J6" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="K6" s="6">
         <v>16</v>
@@ -2054,7 +2051,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="16">
         <f>IFERROR(VLOOKUP($A7,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2085,7 +2082,7 @@
         <v/>
       </c>
       <c r="J7" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7" s="8">
         <f>AVERAGE(B7:B22)</f>
@@ -2094,7 +2091,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="16">
         <f>IFERROR(VLOOKUP($A8,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2125,7 +2122,7 @@
         <v/>
       </c>
       <c r="J8" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K8" s="8">
         <f>AVERAGE(C7:C22)</f>
@@ -2134,7 +2131,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="16">
         <f>IFERROR(VLOOKUP($A9,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2165,7 +2162,7 @@
         <v/>
       </c>
       <c r="J9" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K9" s="8">
         <f>AVERAGE(D7:D22)</f>
@@ -2174,7 +2171,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="16">
         <f>IFERROR(VLOOKUP($A10,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2205,7 +2202,7 @@
         <v/>
       </c>
       <c r="J10" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K10" s="8">
         <f>AVERAGE(G7:G22)</f>
@@ -2214,7 +2211,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="16">
         <f>IFERROR(VLOOKUP($A11,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2245,7 +2242,7 @@
         <v/>
       </c>
       <c r="J11" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K11" s="10">
         <f>MAX(G7:G22)</f>
@@ -2254,7 +2251,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="16">
         <f>IFERROR(VLOOKUP($A12,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2287,7 +2284,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="16">
         <f>IFERROR(VLOOKUP($A13,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2320,7 +2317,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="16">
         <f>IFERROR(VLOOKUP($A14,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2353,7 +2350,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="16">
         <f>IFERROR(VLOOKUP($A15,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2386,7 +2383,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="16">
         <f>IFERROR(VLOOKUP($A16,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2419,7 +2416,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="16">
         <f>IFERROR(VLOOKUP($A17,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2452,7 +2449,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="16">
         <f>IFERROR(VLOOKUP($A18,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2485,7 +2482,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="16">
         <f>IFERROR(VLOOKUP($A19,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2518,7 +2515,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="16">
         <f>IFERROR(VLOOKUP($A20,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2551,7 +2548,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="16">
         <f>IFERROR(VLOOKUP($A21,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -2584,7 +2581,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="17">
         <f>IFERROR(VLOOKUP($A22,'GPS Data'!$A$7:$G$23,2,FALSE),"")</f>
@@ -3026,89 +3023,89 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>52</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
         <v>57</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
         <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -3129,58 +3126,58 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
         <v>69</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
         <v>73</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
         <v>76</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3198,32 +3195,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3241,27 +3238,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Perth_SC_GPS_Weekly_Update_v3.xlsx
+++ b/Perth_SC_GPS_Weekly_Update_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thali/Desktop/Perth_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BFF95D-E5BE-1549-8E5A-2076D8EBD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434C2173-DA20-174E-83C8-657406DA3A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GPS Data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="93">
   <si>
     <t>Perth SC – Senior Women</t>
   </si>
@@ -312,13 +312,19 @@
   </si>
   <si>
     <t>Compare players by soccer role groups: Attackers, Midfielders, and Defenders. Update GPS Data and this dashboard will refresh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail </t>
+  </si>
+  <si>
+    <t>Back injury</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +399,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -512,7 +524,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -561,6 +573,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1050,7 +1063,7 @@
     <col min="5" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="3" customWidth="1"/>
   </cols>
@@ -1107,6 +1120,9 @@
       <c r="H6" s="22" t="s">
         <v>44</v>
       </c>
+      <c r="I6" s="22" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1132,6 +1148,9 @@
       </c>
       <c r="H7" t="s">
         <v>35</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">

--- a/Perth_SC_GPS_Weekly_Update_v3.xlsx
+++ b/Perth_SC_GPS_Weekly_Update_v3.xlsx
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="29" min="1" max="1"/>
@@ -818,7 +818,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -827,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Match</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -837,7 +836,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fremantle City</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -845,8 +849,10 @@
           <t>Round (Game)</t>
         </is>
       </c>
-    </row>
-    <row r="5"/>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -897,61 +903,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. Zindell</t>
+          <t>C. Wainwright</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5774.12</v>
+        <v>12298.64</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>391.54</v>
       </c>
       <c r="D7" t="n">
-        <v>19.58</v>
+        <v>24.03</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>411.35</v>
+        <v>1783.12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Midfielders</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
-          <t>Back injury</t>
-        </is>
-      </c>
+      <c r="I7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. Wainwright</t>
+          <t>D. McAllister</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7291.53</v>
+        <v>10330.9</v>
       </c>
       <c r="C8" t="n">
-        <v>68.36</v>
+        <v>372.4</v>
       </c>
       <c r="D8" t="n">
-        <v>22.78</v>
+        <v>26.14</v>
       </c>
       <c r="E8" t="n">
         <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>856.36</v>
+        <v>1494.13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -966,22 +968,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4313.48</v>
+        <v>5268.91</v>
       </c>
       <c r="C9" t="n">
-        <v>12.03</v>
+        <v>201.83</v>
       </c>
       <c r="D9" t="n">
-        <v>22.26</v>
+        <v>24.29</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>252.24</v>
+        <v>1187.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -992,296 +994,296 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. McAllister</t>
+          <t>E. Lincoln</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5911.91</v>
+        <v>9913.58</v>
       </c>
       <c r="C10" t="n">
-        <v>76.06</v>
+        <v>668.03</v>
       </c>
       <c r="D10" t="n">
-        <v>23.35</v>
+        <v>28.36</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>544.71</v>
+        <v>1681.83</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Midfielders</t>
+          <t>Attackers (8, 9 &amp; 10)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. Ingrey</t>
+          <t>E. Nossent</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4101.67</v>
+        <v>10012.25</v>
       </c>
       <c r="C11" t="n">
-        <v>0.55</v>
+        <v>316</v>
       </c>
       <c r="D11" t="n">
-        <v>19.86</v>
+        <v>26.02</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>245.71</v>
+        <v>1181.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Defenders</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. Lincoln</t>
+          <t>G. Warburton</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6950.08</v>
+        <v>3848.81</v>
       </c>
       <c r="C12" t="n">
-        <v>85.20999999999999</v>
+        <v>386.88</v>
       </c>
       <c r="D12" t="n">
-        <v>24.55</v>
+        <v>28.09</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>478.01</v>
+        <v>802.9400000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Attackers (8</t>
+          <t>Midfielders</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. Nossent</t>
+          <t>J. Flannery</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5939.23</v>
+        <v>11152.83</v>
       </c>
       <c r="C13" t="n">
-        <v>30.93</v>
+        <v>672.17</v>
       </c>
       <c r="D13" t="n">
-        <v>21.64</v>
+        <v>27.93</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>332.93</v>
+        <v>1723.39</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Defenders</t>
+          <t>Attackers (8, 9 &amp; 10)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. Warburton</t>
+          <t>K. Mccartney</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6476.03</v>
+        <v>10788.49</v>
       </c>
       <c r="C14" t="n">
-        <v>40.49</v>
+        <v>283.25</v>
       </c>
       <c r="D14" t="n">
-        <v>20.82</v>
+        <v>27.9</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
-        <v>403.01</v>
+        <v>1129.39</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Midfielders</t>
+          <t>Defenders</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. Flannery</t>
+          <t>L. Tana</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6997.18</v>
+        <v>10095.22</v>
       </c>
       <c r="C15" t="n">
-        <v>80.77</v>
+        <v>458.91</v>
       </c>
       <c r="D15" t="n">
-        <v>25.01</v>
+        <v>27.53</v>
       </c>
       <c r="E15" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="G15" t="n">
-        <v>990.76</v>
+        <v>1599.51</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Attackers (8</t>
+          <t>Defenders</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. Mccartney</t>
+          <t>Macey</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5992.87</v>
+        <v>2939.48</v>
       </c>
       <c r="C16" t="n">
-        <v>29.96</v>
+        <v>261.45</v>
       </c>
       <c r="D16" t="n">
-        <v>26.23</v>
+        <v>22.94</v>
       </c>
       <c r="E16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>311.58</v>
+        <v>530.16</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Defenders</t>
+          <t>Midfielders</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. Continibali</t>
+          <t>M. Boehm</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6066.98</v>
+        <v>10025.86</v>
       </c>
       <c r="C17" t="n">
-        <v>20.23</v>
+        <v>218.23</v>
       </c>
       <c r="D17" t="n">
-        <v>20.52</v>
+        <v>25.83</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>388.21</v>
+        <v>1272.77</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Attackers (8</t>
+          <t>Midfielders</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. Tana</t>
+          <t>R. Marshall</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6342.21</v>
+        <v>10529.03</v>
       </c>
       <c r="C18" t="n">
-        <v>29.97</v>
+        <v>506.45</v>
       </c>
       <c r="D18" t="n">
-        <v>23.32</v>
+        <v>27.41</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>635.58</v>
+        <v>1349.71</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Defenders</t>
+          <t>Attackers (8, 9 &amp; 10)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. Boehm</t>
+          <t>S. Mathers</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6563.66</v>
+        <v>12070.76</v>
       </c>
       <c r="C19" t="n">
-        <v>87.26000000000001</v>
+        <v>749.3200000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>25.29</v>
+        <v>25.9</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
         <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>792.35</v>
+        <v>2167.55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1292,123 +1294,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. Marshall</t>
+          <t>X. Dalton</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7036.88</v>
+        <v>3254.68</v>
       </c>
       <c r="C20" t="n">
-        <v>85.09999999999999</v>
+        <v>223.94</v>
       </c>
       <c r="D20" t="n">
-        <v>26.21</v>
+        <v>23.22</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>981.88</v>
+        <v>555.22</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Attackers (8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S. Mathers</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>6977.62</v>
-      </c>
-      <c r="C21" t="n">
-        <v>73.52</v>
-      </c>
-      <c r="D21" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="E21" t="n">
-        <v>39</v>
-      </c>
-      <c r="F21" t="n">
-        <v>38</v>
-      </c>
-      <c r="G21" t="n">
-        <v>862</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Midfielders</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T. Attree</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>6731.04</v>
-      </c>
-      <c r="C22" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="E22" t="n">
-        <v>44</v>
-      </c>
-      <c r="F22" t="n">
-        <v>68</v>
-      </c>
-      <c r="G22" t="n">
-        <v>741.36</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Defenders</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>X. Dalton</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>6004.46</v>
-      </c>
-      <c r="C23" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="D23" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E23" t="n">
-        <v>25</v>
-      </c>
-      <c r="F23" t="n">
-        <v>22</v>
-      </c>
-      <c r="G23" t="n">
-        <v>646.2</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Attackers (8</t>
-        </is>
-      </c>
-    </row>
+          <t>Attackers (8, 9 &amp; 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="H7:H223" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1586,7 +1501,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M. Boehm</t>
+          <t>Macey</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1705,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M. Boehm</t>
+          <t>Macey</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1861,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>M. Boehm</t>
+          <t>Macey</t>
         </is>
       </c>
     </row>
